--- a/docs/deliverables/out/Drop-2_Independent/TestPlans/BIBS_TestPlan_BRD-08_Employee_Benefits_v1.0.xlsx
+++ b/docs/deliverables/out/Drop-2_Independent/TestPlans/BIBS_TestPlan_BRD-08_Employee_Benefits_v1.0.xlsx
@@ -1352,12 +1352,12 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>The threshold values, measure and approver levels are demo values (EBQ11); the FRS does not say whether "meets" means at or above the amount.</t>
+          <t>The threshold values, measure and approver levels are seed values (EBQ11); the FRS does not say whether "meets" means at or above the amount.</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>State "at or above" and give the BDOI values; the cases use the demo values.</t>
+          <t>State "at or above" and give the BDOI values; the cases use the seed values.</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Role code and name (and demo user for built BRDs)</t>
+          <t>Role code and name (and SIT/UAT user for built BRDs)</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr"/>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Demo seed that provides it (built BRDs) or how to prepare it; non-production data is masked</t>
+          <t>Seed that provides it (built BRDs) or how to prepare it; non-production data is masked</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr"/>
@@ -21559,7 +21559,7 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>Rule 1 all lines, annual premium &gt;= PHP 20,000,000, approver EB_THRESHOLD_APPROVE; rule 2 HMO, TSI &gt;= PHP 500,000,000 (demo values, EBQ11)</t>
+          <t>Rule 1 all lines, annual premium &gt;= PHP 20,000,000, approver EB_THRESHOLD_APPROVE; rule 2 HMO, TSI &gt;= PHP 500,000,000 (seed values, EBQ11)</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
